--- a/Milch.xlsx
+++ b/Milch.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="milch" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="kakao" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="milch" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="kakao" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="zucker" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="263">
   <si>
     <t>Name</t>
   </si>
@@ -233,7 +234,7 @@
     <t>NETTO Gutes Land Kaffeeweißer</t>
   </si>
   <si>
-    <t>Glukosesirup, Kokosfett, Stabilisator: Kaliumphosphate, Polyphosphate; Milcheiweiß, Emulgator: Mono - und Diglyceride von Speisefettsäuren; Trennmittel: Siliciumdioxid</t>
+    <t>Glukosesirup, Kokosfett, Stabilisator: Kaliumphosphate, Polyphosphate, Milcheiweiß, Emulgator: Mono - und Diglyceride von Speisefettsäuren, Trennmittel: Siliciumdioxid</t>
   </si>
   <si>
     <t>KRÜGER Kaffeeweißer</t>
@@ -317,12 +318,18 @@
     <t>ALPRO Sojadrink die Leichte Fettarm</t>
   </si>
   <si>
+    <t>BE</t>
+  </si>
+  <si>
     <t>Wasser, geschälte Sojabohnen (5,6 %), lösliche Maisfasern, Fruktose, Zucker, Calciumcarbonat, Säureregulator (Kaliumphosphate), Meersalz, Aroma, Stabilisator (Gellangummi), Vitamine (B2, B12, D)</t>
   </si>
   <si>
     <t>MY VAY Bio Mandel Drink Hofer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
     <t>Wasser, 2,3 % Mandeln, Maltodextrin, Emulgator: Lecithine, Salz</t>
   </si>
   <si>
@@ -347,7 +354,7 @@
     <t>VEMONDO Bio Kokonuss mit Reis</t>
   </si>
   <si>
-    <t>Wasser, 5,6% Bio Kokosnussmilch, 3,5% Bio Reis, Meersalz, Stabilisatoren: Bio Guarkernmehl, Gellan, Xanthan; natürliches Kokosnuss-Aroma.</t>
+    <t>Wasser, 5,6% Bio Kokosnussmilch, 3,5% Bio Reis, Meersalz, Stabilisatoren: Bio Guarkernmehl, Gellan, Xanthan, natürliches Kokosnuss-Aroma</t>
   </si>
   <si>
     <t>ALPRO Kokos Drink ohne Zucker</t>
@@ -374,6 +381,39 @@
     <t>Wasser, Mandeln (2,5%), Maltodextrin, Emulgator: Lecithine; Meersalz</t>
   </si>
   <si>
+    <t>S-BUDGET Haltbare Magermilch 0,5% Fett</t>
+  </si>
+  <si>
+    <t>Kuhmilch, Kohlenhydrat Milchzucker (Laktose), Eiweiß: Casein, Molkenprotein</t>
+  </si>
+  <si>
+    <t>S-BUDGET Haltbare Fettarme Milch 1,5% Fett</t>
+  </si>
+  <si>
+    <t>S-BUDGET Haltbare Vollmilch 3,5% Fett</t>
+  </si>
+  <si>
+    <t>JA!, H-Milch, entrahmt 0,3%</t>
+  </si>
+  <si>
+    <t>KAUFLAND K-CLASSIC Kaffeeweißer Free</t>
+  </si>
+  <si>
+    <t>Glukosesirup, Kokosfett, Milcheiweiß, Stabilisator: Kaliumphosphat, Emulgator: Mono- und Diglyceride von Speisefettsäuren, Trennmittel: Calciumphosphat</t>
+  </si>
+  <si>
+    <t>Scho No. 207 Topping Vegan</t>
+  </si>
+  <si>
+    <t>Glukosesirup, Kokosfett, Hafermehl 20%, hydrolisiertes Erbsenprotein, Stabilisator (E340ii), Trennmittel (E341iii), Emulgator ( E472e)</t>
+  </si>
+  <si>
+    <t>High Calcium Soy Milk Powder Yon Ho</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
     <t>Malz</t>
   </si>
   <si>
@@ -404,7 +444,7 @@
     <t>MILO</t>
   </si>
   <si>
-    <t>Kakaoschalen Salus</t>
+    <t>Kakaoschalen Salus Bio</t>
   </si>
   <si>
     <t>KAKAO S-BUDGET fettarmer zum Backen</t>
@@ -444,6 +484,324 @@
   </si>
   <si>
     <t>Davert Kakaonibs Bio</t>
+  </si>
+  <si>
+    <t>Dr. Oetker Kakao zum Backen dunkel mit vollmundigem Aroma</t>
+  </si>
+  <si>
+    <t>Cailler Cuisine Kakaopulver</t>
+  </si>
+  <si>
+    <t>Dr. Oetker Schwarzer, Fettarmer Kakao zum Backen</t>
+  </si>
+  <si>
+    <t>Suchard Express Backkakao</t>
+  </si>
+  <si>
+    <t>Bella Kakao Hofer</t>
+  </si>
+  <si>
+    <t>Puda Kakao Penny</t>
+  </si>
+  <si>
+    <t>Kakao Zauberhaft Backen Norma</t>
+  </si>
+  <si>
+    <t>Ülker Kakao</t>
+  </si>
+  <si>
+    <t>TK</t>
+  </si>
+  <si>
+    <t>XUCKER Heisse Schokolade</t>
+  </si>
+  <si>
+    <t>Kalorien</t>
+  </si>
+  <si>
+    <t>Kalt</t>
+  </si>
+  <si>
+    <t>Süsskraft</t>
+  </si>
+  <si>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Typ</t>
+  </si>
+  <si>
+    <t>Stabil</t>
+  </si>
+  <si>
+    <t>Nachteile</t>
+  </si>
+  <si>
+    <t>Mivolis Stevia Tabletten</t>
+  </si>
+  <si>
+    <t>Natur</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Bitter Nachgeschmack</t>
+  </si>
+  <si>
+    <t>Säureregulator Natriumhydrogencarbonat, Säureregulator Natriumcitrate, Süßungsmittel Steviolglycoside aus Stevia (21 %), Trennmittel L–Leucin.</t>
+  </si>
+  <si>
+    <t>Bulk Supplements Aspartam</t>
+  </si>
+  <si>
+    <t>Kunstoff</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Leber Krebs, Diabetes, Herz-Kreislauf-Erkrankungen , Schlaganfälle</t>
+  </si>
+  <si>
+    <t>Beliebten Süssstoff, er so "natürlich" nach Zucker schmeckt.</t>
+  </si>
+  <si>
+    <t>Borchers Sucralose Tabletten</t>
+  </si>
+  <si>
+    <t>DNA-Schädigungen, Blutzuckerspiegel</t>
+  </si>
+  <si>
+    <t>Dextrose, Süßungsmittel: 12 % Sucralose (E 955), vernetzte Carboxymethylcellulose E 468, Vanillearoma.</t>
+  </si>
+  <si>
+    <t>Borchers Sucralose Pulver</t>
+  </si>
+  <si>
+    <t>Maltodextrin, Sucralose.</t>
+  </si>
+  <si>
+    <t>Jeden Tag Tabletten Saccharin</t>
+  </si>
+  <si>
+    <t>Verstopfung</t>
+  </si>
+  <si>
+    <t>Süßungsmittel: 66,7% Cyclamat; Säureregulatoren: Natriumcarbonate, Weinsäure (L+); Süßungsmittel: 6,7% Saccharin.</t>
+  </si>
+  <si>
+    <t>Süsstoff Kandisin Classic Tabletten Saccharin</t>
+  </si>
+  <si>
+    <t>Süßungsmittel Natrium-Cyclamat (E952), Füllstoff Natriumhydrogencarbonat (E500), Süßungsmittel Natrium-Saccharin (E954), Säuerungsmittel Weinsäure (E334).</t>
+  </si>
+  <si>
+    <t>Saporepuro Maltitol Pulver, Maltit</t>
+  </si>
+  <si>
+    <t>Durchfall, Einfluss auf den Blutzuckerspiegel</t>
+  </si>
+  <si>
+    <t>100% MALITIT, Maltitol E965i.</t>
+  </si>
+  <si>
+    <t>Saporepuro SORBIT Pulver</t>
+  </si>
+  <si>
+    <t>Pflanzlich aus Mais oder Kartoffeln.</t>
+  </si>
+  <si>
+    <t>Saporepuro Erythrit Pulver</t>
+  </si>
+  <si>
+    <t>Durchfall, Herzschlag</t>
+  </si>
+  <si>
+    <t>Kalorienfreier, natürlicher Zuckeraustauschstoff aus der Gruppe der Zuckeralkohole, der zu ca. 70 % die Süßkraft von Zucker besitzt. Er wird meist durch Fermentation von Mais gewonnen, schmeckt ähnlich wie Zucker und ist ideal für Diabetiker oder eine Low-Carb-Ernährung, da er den Blutzucker nicht beeinflusst.</t>
+  </si>
+  <si>
+    <t>Saporepuro Xylit Pulver</t>
+  </si>
+  <si>
+    <t>Xylit ursprünglich aus der Rinde von Birken gewonnen wurde.</t>
+  </si>
+  <si>
+    <t>Alnatura Bio Rübenzucker, Saccharose</t>
+  </si>
+  <si>
+    <t>Saccharose (Haushaltszucker) liefert viele Kalorien ohne Nährstoffe, lässt den Blutzuckerspiegel schnell ansteigen und fördert bei übermäßigem Konsum KariesÜbergewicht sowie das Risiko für Typ-2-Diabetes, Herz-Kreislauf-Erkrankungen und Fettleber.</t>
+  </si>
+  <si>
+    <t>Aus Saccharose besteht.</t>
+  </si>
+  <si>
+    <t>Sweet Family Fruktose, Fruchtzucker</t>
+  </si>
+  <si>
+    <t>Einfluss auf den Blutzuckerspiegel, Fördert Diabetes, Gewicht zunahme, schlechte Stoffwechsel. Schlechteste Zucker, in Leber in Fett umgewandelt.</t>
+  </si>
+  <si>
+    <t>Ein natürlicher Einfachzucker, der in Obst, Gemüse und Honig vorkommt.</t>
+  </si>
+  <si>
+    <t>Edelweiss Milchzucker</t>
+  </si>
+  <si>
+    <t>Durchfall und Laktoseintoleranz</t>
+  </si>
+  <si>
+    <t>Aus Laktose.</t>
+  </si>
+  <si>
+    <t>Mivolis Traubenzucker, Dextrose, Glukose</t>
+  </si>
+  <si>
+    <t>Zahnkaries, Durchfall, Blutzucker-Achterbahn &amp; Heißhunger</t>
+  </si>
+  <si>
+    <t>Zutaten: Traubenzucker (91%), Ascorbinsäure (Vitamin C), Nicotinamid, DL-alpha-Tocopherylacetat (Vitamin E), Calcium-D-pantothenat, Pyridoxinhydrochlorid (Vitamin B6), Riboflavin (Vitamin B2), Thiaminmononitrat.(Vitamin)B1),Pteroylmonoglutaminsäure (Folsäure), D-Biotin, Cyanocobalamin (Vitamin B12).</t>
+  </si>
+  <si>
+    <t>Bad Leonhard Maiszucker</t>
+  </si>
+  <si>
+    <t>Fettleber &amp; Stoffwechselerkrankungen, fördert übergewicht</t>
+  </si>
+  <si>
+    <t>Fructosefreie, vegane Alternative zu Haushaltszucker, die aus Maisstärke gewonnen.</t>
+  </si>
+  <si>
+    <t>Grafschafter Goldsaft Zuckerrübensirup, Golden Sirup</t>
+  </si>
+  <si>
+    <t>Sehr hoher Zuckergehalt, nicht für diabetiker</t>
+  </si>
+  <si>
+    <t>Ein naturreiner Zuckerrübensirup. Der Rübensaft wird durch das Abpressen von gekochten Rübenschnitzeln gewonnen.</t>
+  </si>
+  <si>
+    <t>Langnese Flotte Biene Wildblütenhonig</t>
+  </si>
+  <si>
+    <t>fördert Karies und kann den Blutzuckerspiegel stark erhöhen, Antibiotika, Pestiziden</t>
+  </si>
+  <si>
+    <t>Aus dem Nektar verschiedener Wild- und Wiesenblumen.</t>
+  </si>
+  <si>
+    <t>Ahornsirup Grad A DM Drogerie</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Blutzucker schnell ansteigen lässt, nicht stark</t>
+  </si>
+  <si>
+    <t>Eingekochter Saft des kanadischen Zuckerahorns, natürliches veganes Süßungsmittel.</t>
+  </si>
+  <si>
+    <t>Yacon Sirup AcanChia Rohkostqualität</t>
+  </si>
+  <si>
+    <t>Durchfall, wenig intensiv, generiert Oligofruktose</t>
+  </si>
+  <si>
+    <t>Ideal für Diabetiker, aus Yacon Wurzel.</t>
+  </si>
+  <si>
+    <t>Luo Han Guo VitaSanum, Mönchsfrucht Pulver</t>
+  </si>
+  <si>
+    <t>Herz-Kreislauf-Erkrankungen wie Schlaganfälle und Herzinfarkte</t>
+  </si>
+  <si>
+    <t>Eine kleine, grüne Frucht aus Südchina.</t>
+  </si>
+  <si>
+    <t>Rapunzel Zuckerrohr Melasse, Maltose, Malz Zucker</t>
+  </si>
+  <si>
+    <t>Fördert Übergewicht, schadet dem Zahnschmelz</t>
+  </si>
+  <si>
+    <t>Melasse ist ein zäher (hochviskoser) dunkelbrauner Zuckersirup, der als Nebenerzeugnis in der Zuckerproduktion aus Zuckerrohr, Zuckerrüben und auch aus Zuckerhirse anfällt.</t>
+  </si>
+  <si>
+    <t>BIO PRIMO Bio Agavendicksaft Hell</t>
+  </si>
+  <si>
+    <t>Durchfall, fördert Übergewicht, schadet dem Zahnschmelz</t>
+  </si>
+  <si>
+    <t>Süßungsmittel, das auf Basis verschiedener Arten der Agave in Mexiko produziert wird.</t>
+  </si>
+  <si>
+    <t>Acesulfam K DistrEbution</t>
+  </si>
+  <si>
+    <t>Durchfall, negativ Darmmikrobiom, Krebs, Blutzuckerspiegel sowie Stoffwechselprozesse zu beeinflussen, Aftertaste</t>
+  </si>
+  <si>
+    <t>Der Süßstoff ist das Kaliumsalz des Acesulfams, das Acesulfam-Kalium oder Acesulfam.</t>
+  </si>
+  <si>
+    <t>Damhert Tagatesse Dispenser</t>
+  </si>
+  <si>
+    <t>Durchfall, nicht vegan, aus Milchzucker</t>
+  </si>
+  <si>
+    <t>Kommerziell wird D-Tagatose aus Lactose gewonnen.</t>
+  </si>
+  <si>
+    <t>Dillon Organic Chicory Syrup</t>
+  </si>
+  <si>
+    <t>Blähung, wenig süss</t>
+  </si>
+  <si>
+    <t>Oligofruktose, Fruktose, Glukose und Saccharose in Wasser.</t>
+  </si>
+  <si>
+    <t>Bulk Supplements Mannitol Powder</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Durchfall, Reizdarmsyndrom, stark entwässernd wirkt</t>
+  </si>
+  <si>
+    <t>6-wertiger Zuckeralkohol, der als stark osmotisch wirkendes Diuretikum zur Behandlung von Hirnödemen, zur Steigerung der Harnausscheidung (akutes Nierenversagen) und als Süßungsmittel verwendet wird.</t>
+  </si>
+  <si>
+    <t>Lorann Isomalt</t>
+  </si>
+  <si>
+    <t>Durchfall, Reizdarmsyndrom</t>
+  </si>
+  <si>
+    <t>Isomalt ist der einzige Zuckeraustauschstoff, der ausschließlich aus Rübenzucker gewonnen wird.</t>
+  </si>
+  <si>
+    <t>Sucorine Flüssiger Süssstoff Cyclamat</t>
+  </si>
+  <si>
+    <t>Krebs, Darmflora Schaden, Tierversuchen</t>
+  </si>
+  <si>
+    <t>Cyclamat hat einen besonders zuckernahen Geschmack. Wasser, Süssungsmittel: Cyclamat (E 952), Verdickungsmittel: Glycerin (E 422), Konservierungsstoff: Sorbinsäure (E 200).</t>
+  </si>
+  <si>
+    <t>Saporepuro Glukosesirup</t>
+  </si>
+  <si>
+    <t>Hohes Diabetes Risiko, Kein Nährwert, Förderung von Übergewicht, Fett und Stoffwechselstörungen, Blutzuckerspiegel Schwankungen, Karies</t>
+  </si>
+  <si>
+    <t>Billig Dextrose Äquivalent. Dicker, transparenter, farbloser Sirup. Es senkt den Gefrierpunkt und ist ideal ür Gebäck und Eis.</t>
   </si>
 </sst>
 </file>
@@ -480,7 +838,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -491,6 +849,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -505,6 +866,14 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -801,14 +1170,14 @@
         <v>35.0</v>
       </c>
       <c r="K2" s="2">
-        <f t="shared" ref="K2:K49" si="1">J2/I2</f>
+        <f t="shared" ref="K2:K56" si="1">J2/I2</f>
         <v>35</v>
       </c>
       <c r="L2" s="1">
         <v>55.0</v>
       </c>
       <c r="M2" s="2">
-        <f t="shared" ref="M2:M44" si="2">L2/H2</f>
+        <f t="shared" ref="M2:M45" si="2">L2/H2</f>
         <v>1</v>
       </c>
       <c r="N2" s="1">
@@ -2636,7 +3005,7 @@
         <v>100</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>57</v>
@@ -2677,15 +3046,15 @@
         <v>0.13</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>17</v>
@@ -2726,15 +3095,15 @@
         <v>0.12</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>17</v>
@@ -2775,12 +3144,12 @@
         <v>0.2</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>16</v>
@@ -2824,12 +3193,12 @@
         <v>0.12</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>16</v>
@@ -2873,12 +3242,12 @@
         <v>0.13</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>16</v>
@@ -2915,22 +3284,22 @@
         <v>1.9</v>
       </c>
       <c r="M45" s="2">
-        <f t="shared" ref="M45:M49" si="3">L45/$H$45</f>
+        <f t="shared" si="2"/>
         <v>0.7037037037</v>
       </c>
       <c r="N45" s="1">
         <v>0.098</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>17</v>
@@ -2964,22 +3333,21 @@
         <v>0.0</v>
       </c>
       <c r="M46" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N46" s="1">
         <v>0.1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>17</v>
@@ -3013,19 +3381,18 @@
         <v>0.0</v>
       </c>
       <c r="M47" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N47" s="1">
         <v>0.1</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>25</v>
@@ -3062,19 +3429,19 @@
         <v>0.0</v>
       </c>
       <c r="M48" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="M48:M56" si="3">L48/H48</f>
         <v>0</v>
       </c>
       <c r="N48" s="1">
         <v>0.12</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>16</v>
@@ -3112,41 +3479,362 @@
       </c>
       <c r="M49" s="2">
         <f t="shared" si="3"/>
-        <v>0.1851851852</v>
+        <v>0.4166666667</v>
       </c>
       <c r="N49" s="1">
         <v>0.12</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50">
-      <c r="M50" s="3"/>
+      <c r="A50" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>4.9</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J50" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K50" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="L50" s="1">
+        <v>4.9</v>
+      </c>
+      <c r="M50" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="51">
-      <c r="M51" s="3"/>
+      <c r="A51" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>4.9</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J51" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K51" s="2">
+        <f t="shared" si="1"/>
+        <v>2.333333333</v>
+      </c>
+      <c r="L51" s="1">
+        <v>4.9</v>
+      </c>
+      <c r="M51" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="52">
-      <c r="M52" s="3"/>
+      <c r="A52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I52" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J52" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="K52" s="2">
+        <f t="shared" si="1"/>
+        <v>0.9428571429</v>
+      </c>
+      <c r="L52" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="M52" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="53">
-      <c r="M53" s="3"/>
+      <c r="A53" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>5.1</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="J53" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="K53" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L53" s="1">
+        <v>5.1</v>
+      </c>
+      <c r="M53" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="54">
-      <c r="M54" s="3"/>
+      <c r="A54" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="1">
+        <v>514.0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="K54" s="2">
+        <f t="shared" si="1"/>
+        <v>0.0625</v>
+      </c>
+      <c r="L54" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="M54" s="2">
+        <f t="shared" si="3"/>
+        <v>0.1506849315</v>
+      </c>
+      <c r="N54" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="55">
-      <c r="M55" s="3"/>
+      <c r="A55" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="1">
+        <v>502.0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="I55" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="K55" s="2">
+        <f t="shared" si="1"/>
+        <v>0.1461538462</v>
+      </c>
+      <c r="L55" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="M55" s="2">
+        <f t="shared" si="3"/>
+        <v>0.1206349206</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="56">
-      <c r="M56" s="3"/>
+      <c r="A56" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="1">
+        <v>461.0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="K56" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M56" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="57">
-      <c r="M57" s="3"/>
+      <c r="K57" s="2"/>
+      <c r="M57" s="2"/>
     </row>
     <row r="58">
-      <c r="M58" s="3"/>
+      <c r="K58" s="2"/>
+      <c r="M58" s="2"/>
     </row>
     <row r="59">
       <c r="M59" s="3"/>
@@ -5943,15 +6631,6 @@
     </row>
     <row r="990">
       <c r="M990" s="3"/>
-    </row>
-    <row r="991">
-      <c r="M991" s="3"/>
-    </row>
-    <row r="992">
-      <c r="M992" s="3"/>
-    </row>
-    <row r="993">
-      <c r="M993" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5990,7 +6669,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>8</v>
@@ -6010,7 +6689,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
@@ -6042,7 +6721,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -6074,7 +6753,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>37</v>
@@ -6106,7 +6785,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>64</v>
@@ -6138,7 +6817,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>16</v>
@@ -6170,7 +6849,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>37</v>
@@ -6202,7 +6881,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>16</v>
@@ -6234,7 +6913,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>37</v>
@@ -6266,7 +6945,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>27</v>
@@ -6298,7 +6977,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>16</v>
@@ -6330,7 +7009,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>25</v>
@@ -6362,10 +7041,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -6394,7 +7073,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>16</v>
@@ -6426,7 +7105,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>16</v>
@@ -6458,7 +7137,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
@@ -6490,7 +7169,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
@@ -6522,7 +7201,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
@@ -6554,7 +7233,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
@@ -6586,7 +7265,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>64</v>
@@ -6618,7 +7297,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>16</v>
@@ -6650,7 +7329,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
@@ -6682,7 +7361,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
@@ -6710,6 +7389,1539 @@
       </c>
       <c r="J23" s="1">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>369.0</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="I24" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1">
+        <v>368.0</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="I25" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="1">
+        <v>291.0</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I26" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="1">
+        <v>405.0</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="I27" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1">
+        <v>360.0</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>8.7</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I28" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="1">
+        <v>373.0</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="1">
+        <v>20.7</v>
+      </c>
+      <c r="G29" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="I29" s="1">
+        <v>19.9</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="1">
+        <v>357.0</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="1">
+        <v>20.7</v>
+      </c>
+      <c r="G30" s="1">
+        <v>8.8</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I31" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="J31" s="1">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="1">
+        <v>269.0</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="1">
+        <v>4.4</v>
+      </c>
+      <c r="G32" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="43.13"/>
+    <col customWidth="1" min="2" max="2" width="8.0"/>
+    <col customWidth="1" min="3" max="3" width="6.38"/>
+    <col customWidth="1" min="4" max="4" width="4.88"/>
+    <col customWidth="1" min="5" max="5" width="8.38"/>
+    <col customWidth="1" min="6" max="6" width="8.88"/>
+    <col customWidth="1" min="7" max="7" width="5.63"/>
+    <col customWidth="1" min="8" max="8" width="8.13"/>
+    <col customWidth="1" min="9" max="9" width="7.5"/>
+    <col customWidth="1" min="10" max="10" width="11.88"/>
+    <col customWidth="1" min="11" max="11" width="7.0"/>
+    <col customWidth="1" min="12" max="12" width="23.38"/>
+    <col customWidth="1" min="13" max="13" width="18.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1">
+        <v>250.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1">
+        <v>200.0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1">
+        <v>600.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1">
+        <v>600.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1">
+        <v>400.0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1">
+        <v>400.0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="1">
+        <v>210.0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="G8" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="1">
+        <v>260.0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="1">
+        <v>240.0</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="1">
+        <v>387.0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="1">
+        <v>400.0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.99</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="1">
+        <v>380.0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="1">
+        <v>364.0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="G15" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="1">
+        <v>396.0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.99</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" s="1">
+        <v>306.0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="G17" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="1">
+        <v>302.0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="G18" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="1">
+        <v>356.0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="G19" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.89</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="1">
+        <v>197.0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="1">
+        <v>250.0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0.97</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B22" s="1">
+        <v>297.0</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="1">
+        <v>105.0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G23" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="1">
+        <v>200.0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B25" s="1">
+        <v>160.0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B26" s="1">
+        <v>168.0</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B27" s="1">
+        <v>160.0</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0.99</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B28" s="1">
+        <v>240.0</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0.99</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="1">
+        <v>324.0</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0.81</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
